--- a/artfynd/A 51640-2021 artfynd.xlsx
+++ b/artfynd/A 51640-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51640-2021 artfynd.xlsx
+++ b/artfynd/A 51640-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>1330121</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722260.7117204469</v>
+        <v>722261</v>
       </c>
       <c r="R2" t="n">
-        <v>7216005.137558335</v>
+        <v>7216005</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2012-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
